--- a/test.xlsx
+++ b/test.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$X$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -46,8 +48,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,584 +425,585 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>雀魂ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>半庄数</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>总PT</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>总素点</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>平均Naga nishiki 类似度</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>一位数</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>二位数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>三位数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>四位数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TOP率</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>连对率</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>避四率</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>半庄最高打点</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>小局数</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>和牌率</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>放铳率</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>自摸率</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>默和率</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>立直率</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>副露率</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>平均打点</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>平均铳点</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>流局率</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>流听率</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>wzbssjch</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>-22.7</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="1" t="n">
         <v>-7.699999999999999</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="F2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <v>17300</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="2" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2" s="1" t="n">
         <v>5200</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2" s="2" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2" s="2" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>天丁</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>63.8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="1" t="n">
         <v>18.8</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>43800</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="2" t="n">
         <v>0.3571428571428572</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" s="1" t="n">
         <v>6040</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3" s="2" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>冉同学</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1" t="n">
         <v>-41.59999999999999</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="1" t="n">
         <v>-11.6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="1" t="n">
         <v>37700</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="2" t="n">
         <v>0.12</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="2" t="n">
         <v>0.08</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="Q4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4" s="1" t="n">
         <v>8833.333333333334</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4" s="1" t="n">
         <v>8900</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W4" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4" s="2" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>衔蝉幽客</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="1" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="1" t="n">
         <v>28.1</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>42900</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="2" t="n">
         <v>0.08</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="2" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="2" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5" s="1" t="n">
         <v>5985.714285714285</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" s="1" t="n">
         <v>1250</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W5" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X5" s="2" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>奥托维拉</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>-17.1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="1" t="n">
         <v>-2.100000000000001</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="F6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="n">
         <v>22900</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="2" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="2" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" s="2" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6" s="1" t="n">
         <v>5200</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W6" s="2" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X6" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>YIORGOS</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>-65.5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="1" t="n">
         <v>-30.5</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="F7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="n">
         <v>-5500</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="2" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="2" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="Q7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" s="2" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W7" s="2" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X7" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>